--- a/utils/monday_sprint_sprint_2025-24.xlsx
+++ b/utils/monday_sprint_sprint_2025-24.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1651" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1650" uniqueCount="344">
   <si>
     <t>Ticket</t>
   </si>
@@ -141,7 +141,7 @@
     <t>15/10/2024</t>
   </si>
   <si>
-    <t>29/03/2026</t>
+    <t>24/03/2026</t>
   </si>
   <si>
     <t>Outubro</t>
@@ -243,7 +243,7 @@
     <t>11/11/2025</t>
   </si>
   <si>
-    <t>02/03/2026</t>
+    <t>25/02/2026</t>
   </si>
   <si>
     <t>Homologação</t>
@@ -303,6 +303,9 @@
     <t>05/09/2025</t>
   </si>
   <si>
+    <t>19/05/2026</t>
+  </si>
+  <si>
     <t>Setembro</t>
   </si>
   <si>
@@ -408,7 +411,7 @@
     <t>Boa tarde Segue anexo escopo para criação do controle de transferências de Exportação.</t>
   </si>
   <si>
-    <t>25/03/2026</t>
+    <t>20/03/2026</t>
   </si>
   <si>
     <t>35155</t>
@@ -501,7 +504,7 @@
     <t>25/09/2025</t>
   </si>
   <si>
-    <t>15/04/2026</t>
+    <t>10/04/2026</t>
   </si>
   <si>
     <t>34507</t>
@@ -579,7 +582,7 @@
     <t>06/11/2025</t>
   </si>
   <si>
-    <t>14/03/2026</t>
+    <t>09/03/2026</t>
   </si>
   <si>
     <t>34931</t>
@@ -645,7 +648,7 @@
     <t>26/09/2025</t>
   </si>
   <si>
-    <t>25/02/2026</t>
+    <t>20/02/2026</t>
   </si>
   <si>
     <t>34848</t>
@@ -714,7 +717,7 @@
     <t>25/04/2023</t>
   </si>
   <si>
-    <t>23/02/2026</t>
+    <t>18/02/2026</t>
   </si>
   <si>
     <t>Abril</t>
@@ -2474,7 +2477,7 @@
         <v>95</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>17</v>
+        <v>96</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>20</v>
@@ -2483,12 +2486,12 @@
         <v>21</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>15</v>
@@ -2500,22 +2503,22 @@
         <v>36</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>40</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>17</v>
@@ -2527,12 +2530,12 @@
         <v>64</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>15</v>
@@ -2544,10 +2547,10 @@
         <v>17</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>25</v>
@@ -2576,7 +2579,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>15</v>
@@ -2588,10 +2591,10 @@
         <v>17</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>19</v>
@@ -2612,7 +2615,7 @@
         <v>69</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N26" s="2" t="s">
         <v>17</v>
@@ -2620,7 +2623,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>15</v>
@@ -2632,10 +2635,10 @@
         <v>17</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>25</v>
@@ -2664,7 +2667,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>15</v>
@@ -2676,10 +2679,10 @@
         <v>17</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>25</v>
@@ -2708,7 +2711,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>15</v>
@@ -2720,10 +2723,10 @@
         <v>17</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>25</v>
@@ -2752,7 +2755,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>15</v>
@@ -2764,39 +2767,39 @@
         <v>36</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>40</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>17</v>
+        <v>96</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>15</v>
@@ -2808,10 +2811,10 @@
         <v>17</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>25</v>
@@ -2840,7 +2843,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>15</v>
@@ -2852,10 +2855,10 @@
         <v>17</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>19</v>
@@ -2896,10 +2899,10 @@
         <v>17</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>25</v>
@@ -2928,7 +2931,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>15</v>
@@ -2940,10 +2943,10 @@
         <v>17</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>25</v>
@@ -2972,7 +2975,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>15</v>
@@ -2984,10 +2987,10 @@
         <v>17</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>25</v>
@@ -3016,7 +3019,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>15</v>
@@ -3028,25 +3031,25 @@
         <v>36</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>40</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>33</v>
@@ -3055,12 +3058,12 @@
         <v>64</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>15</v>
@@ -3072,10 +3075,10 @@
         <v>17</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>25</v>
@@ -3104,7 +3107,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>15</v>
@@ -3116,25 +3119,25 @@
         <v>36</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>62</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>28</v>
@@ -3148,7 +3151,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>15</v>
@@ -3160,10 +3163,10 @@
         <v>17</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>25</v>
@@ -3204,10 +3207,10 @@
         <v>17</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>19</v>
@@ -3236,7 +3239,7 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>15</v>
@@ -3248,22 +3251,22 @@
         <v>36</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>62</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K41" s="2" t="s">
         <v>76</v>
@@ -3275,12 +3278,12 @@
         <v>34</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>15</v>
@@ -3292,10 +3295,10 @@
         <v>17</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>25</v>
@@ -3316,7 +3319,7 @@
         <v>28</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N42" s="2" t="s">
         <v>17</v>
@@ -3324,7 +3327,7 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>15</v>
@@ -3336,22 +3339,22 @@
         <v>36</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>62</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K43" s="2" t="s">
         <v>17</v>
@@ -3368,7 +3371,7 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>15</v>
@@ -3380,25 +3383,25 @@
         <v>36</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>62</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>77</v>
@@ -3407,12 +3410,12 @@
         <v>64</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>15</v>
@@ -3424,10 +3427,10 @@
         <v>17</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>25</v>
@@ -3456,7 +3459,7 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>15</v>
@@ -3468,10 +3471,10 @@
         <v>17</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>19</v>
@@ -3500,7 +3503,7 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>15</v>
@@ -3512,10 +3515,10 @@
         <v>17</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>25</v>
@@ -3544,7 +3547,7 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>15</v>
@@ -3556,22 +3559,22 @@
         <v>36</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>62</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K48" s="2" t="s">
         <v>17</v>
@@ -3600,10 +3603,10 @@
         <v>17</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>19</v>
@@ -3632,7 +3635,7 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>15</v>
@@ -3644,22 +3647,22 @@
         <v>36</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>62</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K50" s="2" t="s">
         <v>76</v>
@@ -3671,12 +3674,12 @@
         <v>34</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>15</v>
@@ -3688,10 +3691,10 @@
         <v>17</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>25</v>
@@ -3720,7 +3723,7 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>15</v>
@@ -3732,10 +3735,10 @@
         <v>17</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>25</v>
@@ -3764,7 +3767,7 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>15</v>
@@ -3776,25 +3779,25 @@
         <v>36</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>40</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L53" s="2" t="s">
         <v>20</v>
@@ -3808,7 +3811,7 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>15</v>
@@ -3820,25 +3823,25 @@
         <v>36</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>40</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L54" s="2" t="s">
         <v>28</v>
@@ -3852,7 +3855,7 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>15</v>
@@ -3864,10 +3867,10 @@
         <v>17</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>25</v>
@@ -3896,7 +3899,7 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>15</v>
@@ -3908,10 +3911,10 @@
         <v>17</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>25</v>
@@ -3940,7 +3943,7 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>15</v>
@@ -3952,10 +3955,10 @@
         <v>17</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>25</v>
@@ -3984,7 +3987,7 @@
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>15</v>
@@ -3996,16 +3999,16 @@
         <v>36</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>62</v>
@@ -4023,12 +4026,12 @@
         <v>21</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>15</v>
@@ -4040,10 +4043,10 @@
         <v>17</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>19</v>
@@ -4072,7 +4075,7 @@
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>15</v>
@@ -4084,25 +4087,25 @@
         <v>36</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>62</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L60" s="2" t="s">
         <v>20</v>
@@ -4111,12 +4114,12 @@
         <v>64</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>15</v>
@@ -4128,10 +4131,10 @@
         <v>17</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>19</v>
@@ -4160,7 +4163,7 @@
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>15</v>
@@ -4172,13 +4175,13 @@
         <v>17</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>17</v>
@@ -4204,7 +4207,7 @@
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>15</v>
@@ -4216,10 +4219,10 @@
         <v>17</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>25</v>
@@ -4248,7 +4251,7 @@
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>15</v>
@@ -4260,10 +4263,10 @@
         <v>17</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>25</v>
@@ -4292,7 +4295,7 @@
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>15</v>
@@ -4304,10 +4307,10 @@
         <v>17</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>25</v>
@@ -4380,7 +4383,7 @@
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>15</v>
@@ -4392,10 +4395,10 @@
         <v>17</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>19</v>
@@ -4424,7 +4427,7 @@
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>15</v>
@@ -4436,22 +4439,22 @@
         <v>36</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I68" s="2" t="s">
         <v>62</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K68" s="2" t="s">
         <v>76</v>
@@ -4468,7 +4471,7 @@
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>15</v>
@@ -4480,25 +4483,25 @@
         <v>36</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>62</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L69" s="2" t="s">
         <v>69</v>
@@ -4507,12 +4510,12 @@
         <v>64</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>15</v>
@@ -4524,10 +4527,10 @@
         <v>17</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>25</v>
@@ -4556,7 +4559,7 @@
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>15</v>
@@ -4568,10 +4571,10 @@
         <v>17</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>25</v>
@@ -4600,7 +4603,7 @@
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>15</v>
@@ -4612,10 +4615,10 @@
         <v>17</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>25</v>
@@ -4644,7 +4647,7 @@
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>15</v>
@@ -4656,10 +4659,10 @@
         <v>17</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>25</v>
@@ -4688,7 +4691,7 @@
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>15</v>
@@ -4700,10 +4703,10 @@
         <v>17</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>25</v>
@@ -4732,7 +4735,7 @@
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>15</v>
@@ -4744,10 +4747,10 @@
         <v>17</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>25</v>
@@ -4776,7 +4779,7 @@
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>15</v>
@@ -4788,10 +4791,10 @@
         <v>17</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>25</v>
@@ -4820,7 +4823,7 @@
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>15</v>
@@ -4832,25 +4835,25 @@
         <v>36</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I77" s="2" t="s">
         <v>62</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L77" s="2" t="s">
         <v>28</v>
@@ -4864,7 +4867,7 @@
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>15</v>
@@ -4876,10 +4879,10 @@
         <v>17</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>25</v>
@@ -4908,7 +4911,7 @@
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>15</v>
@@ -4920,10 +4923,10 @@
         <v>17</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>25</v>
@@ -4952,7 +4955,7 @@
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>15</v>
@@ -4964,10 +4967,10 @@
         <v>17</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>25</v>
@@ -4996,7 +4999,7 @@
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>15</v>
@@ -5008,10 +5011,10 @@
         <v>17</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>25</v>
@@ -5052,7 +5055,7 @@
         <v>36</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>17</v>
@@ -5096,10 +5099,10 @@
         <v>17</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>25</v>
@@ -5140,7 +5143,7 @@
         <v>36</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>17</v>
@@ -5184,7 +5187,7 @@
         <v>36</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>17</v>
@@ -5228,10 +5231,10 @@
         <v>17</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>19</v>
@@ -5272,7 +5275,7 @@
         <v>36</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>17</v>
@@ -5304,7 +5307,7 @@
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>15</v>
@@ -5316,22 +5319,22 @@
         <v>36</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I88" s="2" t="s">
         <v>62</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K88" s="2" t="s">
         <v>17</v>
@@ -5343,12 +5346,12 @@
         <v>29</v>
       </c>
       <c r="N88" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>15</v>
@@ -5360,10 +5363,10 @@
         <v>17</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>25</v>
@@ -5404,10 +5407,10 @@
         <v>17</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>25</v>
@@ -5448,7 +5451,7 @@
         <v>36</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>17</v>
@@ -5492,10 +5495,10 @@
         <v>17</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>25</v>
@@ -5536,10 +5539,10 @@
         <v>17</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>25</v>
@@ -5568,7 +5571,7 @@
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>15</v>
@@ -5580,10 +5583,10 @@
         <v>17</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>25</v>
@@ -5624,10 +5627,10 @@
         <v>17</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>25</v>
@@ -5668,10 +5671,10 @@
         <v>17</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>25</v>
@@ -5700,7 +5703,7 @@
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>15</v>
@@ -5712,10 +5715,10 @@
         <v>17</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>19</v>
@@ -5744,7 +5747,7 @@
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>15</v>
@@ -5756,10 +5759,10 @@
         <v>17</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>25</v>
@@ -5777,7 +5780,7 @@
         <v>17</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M98" s="2" t="s">
         <v>29</v>
@@ -5788,7 +5791,7 @@
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>15</v>
@@ -5800,39 +5803,39 @@
         <v>36</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I99" s="2" t="s">
         <v>40</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>17</v>
+        <v>96</v>
       </c>
       <c r="L99" s="2" t="s">
         <v>28</v>
       </c>
       <c r="M99" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N99" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>15</v>
@@ -5844,10 +5847,10 @@
         <v>17</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>25</v>
@@ -5876,7 +5879,7 @@
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>15</v>
@@ -5888,39 +5891,39 @@
         <v>36</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I101" s="2" t="s">
         <v>40</v>
       </c>
       <c r="J101" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K101" s="2" t="s">
-        <v>17</v>
+        <v>96</v>
       </c>
       <c r="L101" s="2" t="s">
         <v>28</v>
       </c>
       <c r="M101" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N101" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>15</v>
@@ -5932,10 +5935,10 @@
         <v>17</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>19</v>
@@ -5964,7 +5967,7 @@
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>15</v>
@@ -5976,10 +5979,10 @@
         <v>17</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>25</v>
@@ -6008,7 +6011,7 @@
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>15</v>
@@ -6020,10 +6023,10 @@
         <v>17</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="G104" s="2" t="s">
         <v>25</v>
@@ -6052,7 +6055,7 @@
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>15</v>
@@ -6064,10 +6067,10 @@
         <v>17</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="G105" s="2" t="s">
         <v>25</v>
@@ -6096,7 +6099,7 @@
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>15</v>
@@ -6108,10 +6111,10 @@
         <v>17</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="G106" s="2" t="s">
         <v>25</v>
@@ -6140,7 +6143,7 @@
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>15</v>
@@ -6152,10 +6155,10 @@
         <v>17</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>25</v>
@@ -6184,7 +6187,7 @@
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>15</v>
@@ -6196,10 +6199,10 @@
         <v>17</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="G108" s="2" t="s">
         <v>25</v>
@@ -6228,7 +6231,7 @@
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>15</v>
@@ -6240,10 +6243,10 @@
         <v>17</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G109" s="2" t="s">
         <v>25</v>
@@ -6272,7 +6275,7 @@
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>15</v>
@@ -6284,10 +6287,10 @@
         <v>17</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G110" s="2" t="s">
         <v>25</v>
@@ -6316,7 +6319,7 @@
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>15</v>
@@ -6328,10 +6331,10 @@
         <v>36</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G111" s="2" t="s">
         <v>25</v>
@@ -6343,10 +6346,10 @@
         <v>62</v>
       </c>
       <c r="J111" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K111" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L111" s="2" t="s">
         <v>28</v>
@@ -6355,12 +6358,12 @@
         <v>29</v>
       </c>
       <c r="N111" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>15</v>
@@ -6372,10 +6375,10 @@
         <v>17</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="G112" s="2" t="s">
         <v>25</v>
@@ -6415,23 +6418,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -6439,16 +6442,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -6467,7 +6470,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -6488,7 +6491,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -6519,12 +6522,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B2">
         <v>111</v>
@@ -6548,25 +6551,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -6583,13 +6586,13 @@
         <v>93</v>
       </c>
       <c r="G10" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -6604,7 +6607,7 @@
         <v>21</v>
       </c>
       <c r="Q10">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
@@ -6621,7 +6624,7 @@
         <v>29</v>
       </c>
       <c r="J11" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K11">
         <v>111</v>
@@ -6653,7 +6656,7 @@
         <v>80</v>
       </c>
       <c r="M12" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N12">
         <v>1</v>
@@ -6662,7 +6665,7 @@
         <v>29</v>
       </c>
       <c r="Q12">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="4:17" x14ac:dyDescent="0.25">
@@ -6673,7 +6676,7 @@
         <v>3</v>
       </c>
       <c r="G13" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H13">
         <v>2</v>
@@ -6688,10 +6691,10 @@
         <v>64</v>
       </c>
       <c r="Q13">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="4:17" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D14" t="s">
         <v>16</v>
       </c>
@@ -6699,7 +6702,7 @@
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -6709,12 +6712,6 @@
       </c>
       <c r="N14">
         <v>9</v>
-      </c>
-      <c r="P14" t="s">
-        <v>107</v>
-      </c>
-      <c r="Q14">
-        <v>1</v>
       </c>
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
@@ -6727,7 +6724,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -6735,7 +6732,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -6743,7 +6740,7 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
@@ -6754,7 +6751,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -6762,44 +6759,44 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F21" s="2">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F22" s="2">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F23" s="2">
-        <v>715</v>
+        <v>709</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6810,7 +6807,7 @@
         <v>15</v>
       </c>
       <c r="F24" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>37</v>
@@ -6818,35 +6815,35 @@
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>114</v>
+        <v>288</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F25" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>115</v>
+        <v>289</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F26" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>287</v>
+        <v>115</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>15</v>
@@ -6855,21 +6852,21 @@
         <v>458</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>288</v>
+        <v>116</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F28" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6880,7 +6877,7 @@
         <v>15</v>
       </c>
       <c r="F29" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>60</v>
@@ -6894,7 +6891,7 @@
         <v>15</v>
       </c>
       <c r="F30" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>60</v>

--- a/utils/monday_sprint_sprint_2025-24.xlsx
+++ b/utils/monday_sprint_sprint_2025-24.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1767" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1769" uniqueCount="341">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>28708</t>
+    <t>18330967622</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,163 +87,169 @@
     <t>03/11/2025</t>
   </si>
   <si>
+    <t>17/11/2025</t>
+  </si>
+  <si>
+    <t>Feito</t>
+  </si>
+  <si>
+    <t>Não</t>
+  </si>
+  <si>
+    <t>Semana 1</t>
+  </si>
+  <si>
+    <t>Novembro</t>
+  </si>
+  <si>
+    <t>18331067527</t>
+  </si>
+  <si>
+    <t>Melhoria</t>
+  </si>
+  <si>
+    <t>Manter data/hora de inclusão e data/Hora de alteração.</t>
+  </si>
+  <si>
+    <t>Média</t>
+  </si>
+  <si>
+    <t>18236205098</t>
+  </si>
+  <si>
+    <t>Calculo do custo de embalagens</t>
+  </si>
+  <si>
+    <t>21/10/2025</t>
+  </si>
+  <si>
+    <t>A fazer</t>
+  </si>
+  <si>
+    <t>Semana 3</t>
+  </si>
+  <si>
+    <t>Outubro</t>
+  </si>
+  <si>
+    <t>18379269547</t>
+  </si>
+  <si>
+    <t>Correção</t>
+  </si>
+  <si>
+    <t>WMS x empilhadeira grande</t>
+  </si>
+  <si>
+    <t>14/11/2025</t>
+  </si>
+  <si>
+    <t>25/11/2025</t>
+  </si>
+  <si>
+    <t>Implantação</t>
+  </si>
+  <si>
+    <t>Semana 2</t>
+  </si>
+  <si>
+    <t>28392</t>
+  </si>
+  <si>
+    <t>Contabilidade</t>
+  </si>
+  <si>
+    <t>Solicitação de serviço</t>
+  </si>
+  <si>
+    <t>Notas de consignado - Medição NIMBI</t>
+  </si>
+  <si>
+    <t>Bom dia, Conforme reunião dia 10/10 com o Sandro, queremos solicitar uma alteração no sistema de consignados da empresa. Sobre os contratos de consignado será gerado uma ordem de compra, e dentro dessas ordens terão medições para os consumos dos consignados. Para verificar que a OC é referente a con</t>
+  </si>
+  <si>
+    <t>Jessica Priscila Gonçalves</t>
+  </si>
+  <si>
+    <t>ADH</t>
+  </si>
+  <si>
+    <t>25/10/2024</t>
+  </si>
+  <si>
+    <t>24/03/2026</t>
+  </si>
+  <si>
+    <t>Semana 4</t>
+  </si>
+  <si>
+    <t>18330872529</t>
+  </si>
+  <si>
+    <t>Cálculo de carga - Sistema de corridas</t>
+  </si>
+  <si>
+    <t>18379281205</t>
+  </si>
+  <si>
+    <t>APONTAMENTO ELETRONICO MESA REDONDA</t>
+  </si>
+  <si>
+    <t>18/11/2025</t>
+  </si>
+  <si>
+    <t>10577840814</t>
+  </si>
+  <si>
+    <t>Atualização de Metas - Local - Apresentação</t>
+  </si>
+  <si>
+    <t>18236205317</t>
+  </si>
+  <si>
+    <t>Cálculo de Horas para o BI por Macro área - Revisar a fórmula do cálculo de em todas as macro áreas (copy) (copy)</t>
+  </si>
+  <si>
+    <t>18331016037</t>
+  </si>
+  <si>
+    <t>Auditoria MPO, PID e Checklist</t>
+  </si>
+  <si>
+    <t>10577840720</t>
+  </si>
+  <si>
+    <t>Chamado para revisão BI Manutenção - Chamado Principal</t>
+  </si>
+  <si>
+    <t>10577792855</t>
+  </si>
+  <si>
+    <t>Criar campo para gatilho de analise de causa raiz</t>
+  </si>
+  <si>
+    <t>33130</t>
+  </si>
+  <si>
+    <t>Comercial</t>
+  </si>
+  <si>
+    <t>Projeto</t>
+  </si>
+  <si>
+    <t>Cadastro de cliente</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
-    <t>Feito</t>
-  </si>
-  <si>
-    <t>Não</t>
-  </si>
-  <si>
-    <t>Semana 1</t>
-  </si>
-  <si>
-    <t>Novembro</t>
-  </si>
-  <si>
-    <t>33333</t>
-  </si>
-  <si>
-    <t>Melhoria</t>
-  </si>
-  <si>
-    <t>Manter data/hora de inclusão e data/Hora de alteração.</t>
-  </si>
-  <si>
-    <t>Média</t>
-  </si>
-  <si>
-    <t>27379</t>
-  </si>
-  <si>
-    <t>Calculo do custo de embalagens</t>
-  </si>
-  <si>
-    <t>21/10/2025</t>
-  </si>
-  <si>
-    <t>A fazer</t>
-  </si>
-  <si>
-    <t>Aberto</t>
-  </si>
-  <si>
-    <t>Semana 3</t>
-  </si>
-  <si>
-    <t>Outubro</t>
-  </si>
-  <si>
-    <t>35221</t>
-  </si>
-  <si>
-    <t>Correção</t>
-  </si>
-  <si>
-    <t>WMS x empilhadeira grande</t>
-  </si>
-  <si>
-    <t>14/11/2025</t>
-  </si>
-  <si>
-    <t>Implantação</t>
-  </si>
-  <si>
-    <t>Semana 2</t>
-  </si>
-  <si>
-    <t>28392</t>
-  </si>
-  <si>
-    <t>Solicitação de serviço</t>
-  </si>
-  <si>
-    <t>Notas de consignado - Medição NIMBI</t>
-  </si>
-  <si>
-    <t>Bom dia, Conforme reunião dia 10/10 com o Sandro, queremos solicitar uma alteração no sistema de consignados da empresa. Sobre os contratos de consignado será gerado uma ordem de compra, e dentro dessas ordens terão medições para os consumos dos consignados. Para verificar que a OC é referente a con</t>
-  </si>
-  <si>
-    <t>Jessica Priscila Gonçalves</t>
-  </si>
-  <si>
-    <t>ADH</t>
-  </si>
-  <si>
-    <t>25/10/2024</t>
-  </si>
-  <si>
-    <t>24/03/2026</t>
-  </si>
-  <si>
-    <t>Semana 4</t>
-  </si>
-  <si>
-    <t>33632</t>
-  </si>
-  <si>
-    <t>Cálculo de carga - Sistema de corridas</t>
-  </si>
-  <si>
-    <t>35186</t>
-  </si>
-  <si>
-    <t>APONTAMENTO ELETRONICO MESA REDONDA</t>
-  </si>
-  <si>
-    <t>33412</t>
-  </si>
-  <si>
-    <t>Atualização de Metas - Local - Apresentação</t>
-  </si>
-  <si>
-    <t>17/11/2025</t>
-  </si>
-  <si>
-    <t>24641</t>
-  </si>
-  <si>
-    <t>Cálculo de Horas para o BI por Macro área - Revisar a fórmula do cálculo de em todas as macro áreas (copy) (copy)</t>
-  </si>
-  <si>
-    <t>33360</t>
-  </si>
-  <si>
-    <t>Auditoria MPO, PID e Checklist</t>
-  </si>
-  <si>
-    <t>34793</t>
-  </si>
-  <si>
-    <t>Chamado para revisão BI Manutenção - Chamado Principal</t>
-  </si>
-  <si>
-    <t>33933</t>
-  </si>
-  <si>
-    <t>Criar campo para gatilho de analise de causa raiz</t>
-  </si>
-  <si>
-    <t>33130</t>
-  </si>
-  <si>
-    <t>Comercial</t>
-  </si>
-  <si>
-    <t>Projeto</t>
-  </si>
-  <si>
-    <t>Cadastro de cliente</t>
-  </si>
-  <si>
     <t>Laura Herrmann Schmickler</t>
   </si>
   <si>
     <t>Sistemas</t>
   </si>
   <si>
-    <t>23838</t>
+    <t>18236205216</t>
   </si>
   <si>
     <t>Novo Sistema</t>
@@ -252,13 +258,19 @@
     <t>Inclusão dos novos pátios</t>
   </si>
   <si>
+    <t>27/11/2025</t>
+  </si>
+  <si>
     <t>Fazendo</t>
   </si>
   <si>
+    <t>18331067194</t>
+  </si>
+  <si>
     <t>Teste com Trigger - Checagem do fechamento do custo</t>
   </si>
   <si>
-    <t>35206</t>
+    <t>18379279100</t>
   </si>
   <si>
     <t>Alterações nas etiquetas de moldagem</t>
@@ -267,28 +279,34 @@
     <t>Homologação</t>
   </si>
   <si>
-    <t>32677</t>
+    <t>18236205336</t>
   </si>
   <si>
     <t>PDI - Fixar colunas de identificação das cotas</t>
   </si>
   <si>
-    <t>34053</t>
+    <t>18236205713</t>
   </si>
   <si>
     <t>Melhoria Sistema de Custeio - INSERTOS</t>
   </si>
   <si>
+    <t>18236204949</t>
+  </si>
+  <si>
     <t>Reorganizar filtro x campos na tela de visão master</t>
   </si>
   <si>
-    <t>34109</t>
+    <t>10577793002</t>
   </si>
   <si>
     <t>Melhorias Sistema Manutenção - Apresentação</t>
   </si>
   <si>
-    <t>32839</t>
+    <t>24/11/2025</t>
+  </si>
+  <si>
+    <t>9571834732</t>
   </si>
   <si>
     <t>[NIMBI] ATUALIZAÇÃO PARA ALTERAÇÃO DE PEDIDO</t>
@@ -297,12 +315,18 @@
     <t>11/07/2025</t>
   </si>
   <si>
+    <t>23/11/2025</t>
+  </si>
+  <si>
     <t>Julho</t>
   </si>
   <si>
     <t>33956</t>
   </si>
   <si>
+    <t>Manutenção</t>
+  </si>
+  <si>
     <t>Definição de metas de custos de manutenção (META GERAL)</t>
   </si>
   <si>
@@ -318,6 +342,9 @@
     <t>25310</t>
   </si>
   <si>
+    <t>Logística</t>
+  </si>
+  <si>
     <t>Sistema de Controle de Orçamento de Entregas de Venda (copy)</t>
   </si>
   <si>
@@ -327,13 +354,13 @@
     <t>Djalma Machado</t>
   </si>
   <si>
-    <t>33271</t>
+    <t>18236205993</t>
   </si>
   <si>
     <t>Alinhamento dos cálculos de disponibilidade</t>
   </si>
   <si>
-    <t>34952</t>
+    <t>18321210125</t>
   </si>
   <si>
     <t>Criação Relatório BI ProfMix</t>
@@ -342,22 +369,25 @@
     <t>31/10/2025</t>
   </si>
   <si>
+    <t>26/11/2025</t>
+  </si>
+  <si>
     <t>Semana 5</t>
   </si>
   <si>
-    <t>34595</t>
+    <t>10577991268</t>
   </si>
   <si>
     <t>PID Rejeitando cotas Aprovadas (copy)</t>
   </si>
   <si>
-    <t>35130</t>
+    <t>18379320099</t>
   </si>
   <si>
     <t>Correções layout aplicação de faseamento de vendas</t>
   </si>
   <si>
-    <t>35157</t>
+    <t>18379284367</t>
   </si>
   <si>
     <t>Reabertura de O.S. corretiva</t>
@@ -372,28 +402,34 @@
     <t>Boa tarde Precisamos que seja realizada a alteração do sistema abaixo onde faz a busca das etiquetas amarelas para os romaneios "ATIVO", desconsiderando o BOX 0. Deve aparecer disponível para vincular no ticket todos os romaneios do modelo/conjunto conforme as regras atuais do sistema. Também deve s</t>
   </si>
   <si>
-    <t>34027</t>
+    <t>10577994149</t>
   </si>
   <si>
     <t>LOG TRANSFERENCIA NO SISTEMA INVOICE - AJUSTE SISTEMA GESTÃO A VISTA (copy)</t>
   </si>
   <si>
-    <t>34534</t>
+    <t>10577844020</t>
   </si>
   <si>
     <t>Indicadores de Setup - IROG Usinagem</t>
   </si>
   <si>
+    <t>01/12/2025</t>
+  </si>
+  <si>
+    <t>18334943817</t>
+  </si>
+  <si>
     <t>Importar planilha gerencial</t>
   </si>
   <si>
-    <t>34942</t>
+    <t>10577997731</t>
   </si>
   <si>
     <t>Certificados de Qualidade (copy)</t>
   </si>
   <si>
-    <t>34676</t>
+    <t>18212336974</t>
   </si>
   <si>
     <t>Melhoria Sistema de Custeio - Materiais Secundários</t>
@@ -414,12 +450,15 @@
     <t>20/03/2026</t>
   </si>
   <si>
-    <t>35155</t>
+    <t>18379311190</t>
   </si>
   <si>
     <t>TELA DE CRIAÇÃO DE CPPs POR CÓPIA</t>
   </si>
   <si>
+    <t>20/11/2025</t>
+  </si>
+  <si>
     <t>34720</t>
   </si>
   <si>
@@ -441,22 +480,28 @@
     <t>02/04/2026</t>
   </si>
   <si>
-    <t>34761</t>
+    <t>18213853293</t>
   </si>
   <si>
     <t>Agrupar Relatório - Modelos Bloqueados</t>
   </si>
   <si>
+    <t>19/11/2025</t>
+  </si>
+  <si>
+    <t>10577842388</t>
+  </si>
+  <si>
     <t>Campo calculado de % Disponibilidade / MTTR e MTBF</t>
   </si>
   <si>
-    <t>33387</t>
+    <t>10577994445</t>
   </si>
   <si>
     <t>HORIMETRO MANIPULADORES (copy)</t>
   </si>
   <si>
-    <t>34378</t>
+    <t>18322007271</t>
   </si>
   <si>
     <t>BI análise de ofertas - add metas</t>
@@ -492,13 +537,16 @@
     <t>10/04/2026</t>
   </si>
   <si>
-    <t>34507</t>
+    <t>18330871496</t>
   </si>
   <si>
     <t>Altona || Consignado - Conferência Fornecedores</t>
   </si>
   <si>
-    <t>33604</t>
+    <t>30/11/2025</t>
+  </si>
+  <si>
+    <t>9985884121</t>
   </si>
   <si>
     <t>Aplicação “retrabalho global” demora muito para carregar</t>
@@ -510,85 +558,70 @@
     <t>Setembro</t>
   </si>
   <si>
-    <t>29123</t>
+    <t>10577840434</t>
   </si>
   <si>
     <t>B.I ordens de manutenção maquinas pneumáticas</t>
   </si>
   <si>
-    <t>34599</t>
+    <t>18321837848</t>
   </si>
   <si>
     <t>Sistema de Embalagens - Relatório Requisição Embalagem por Sequência</t>
   </si>
   <si>
-    <t>Bom dia Sandro. Cristian me passou que o desenvolvimento do sistema para gestão de Embalagem está concluído. Ótima notícia. Desenvolver relatório conforme layout no anexo. Relatório será de período fechado de mês, após o fechamento do mês. Listar mesmo as requisições que não tenham vinculadas etique</t>
-  </si>
-  <si>
-    <t>Paulo Giovani da Cruz</t>
+    <t>10577842665</t>
   </si>
   <si>
     <t>Corrigir duplicidade de dados na base da aplicação</t>
   </si>
   <si>
-    <t>34012</t>
+    <t>10577859112</t>
   </si>
   <si>
     <t>Painel de indicadores + Melhorias - Sistema Manutenção</t>
   </si>
   <si>
-    <t>34555</t>
+    <t>18212504836</t>
   </si>
   <si>
     <t>Preciso de um relatório para extrair as sequencias estornadas do refugo</t>
   </si>
   <si>
-    <t>35145</t>
+    <t>18379317749</t>
   </si>
   <si>
     <t>Atualização da tela materiais endereçados</t>
   </si>
   <si>
-    <t>35128</t>
+    <t>18379322922</t>
   </si>
   <si>
     <t>Altona || Conferência Entrada de Consignados - Melhoria</t>
   </si>
   <si>
-    <t>Bom dia, Sandro! Dando continuidade ao processo de melhoria nas conferências do estoque peço que insiras no relatório abaixo: duas colunas conforme descrição abaixo e planilha anexa: 1) Finalidade (MP/C) - esse parâmetro servirá para conferir se um produto está classificado corretamente e consequent</t>
-  </si>
-  <si>
-    <t>09/03/2026</t>
-  </si>
-  <si>
-    <t>34931</t>
+    <t>18376432514</t>
   </si>
   <si>
     <t>Corrigir Cálculo do Custo de Bloqueios</t>
   </si>
   <si>
-    <t>Boa tarde Sandro. Código Descrição Matéria Prima 100579 SUCATA BLOQUEIO EA-16001 CF3 100587 SUCATA BLOQUEIO EA-16002 CF3M 100722 SUCATA BLOQUEIO EA-16007 CA6NM 100922 SUCATA BLOQUEIO EA-16019 102467 SUCATA BLOQUEIO EA-16020</t>
-  </si>
-  <si>
     <t>12/11/2025</t>
   </si>
   <si>
-    <t>10/03/2026</t>
-  </si>
-  <si>
-    <t>33395</t>
+    <t>18376441636</t>
   </si>
   <si>
     <t>Ordens de Compra - Benner</t>
   </si>
   <si>
-    <t>33009</t>
+    <t>10578065782</t>
   </si>
   <si>
     <t>Ajustes Dalca e Lianco</t>
   </si>
   <si>
-    <t>35125</t>
+    <t>18379327447</t>
   </si>
   <si>
     <t>ATUALIZAÇÃO TELA MODELO UNIVERSAL</t>
@@ -609,100 +642,103 @@
     <t>Matheus Rodrigues de Almeida</t>
   </si>
   <si>
-    <t>34073</t>
+    <t>10578066176</t>
   </si>
   <si>
     <t>Siga - Consulta Sequencia (Alt c)</t>
   </si>
   <si>
-    <t>34377</t>
+    <t>18330872054</t>
   </si>
   <si>
     <t>Lógica de ACR no sistema de manutenção - Pila 2 MP</t>
   </si>
   <si>
-    <t>34848</t>
+    <t>18379412607</t>
   </si>
   <si>
     <t>Erro no cadastro do tempo padrão</t>
   </si>
   <si>
-    <t>34723</t>
+    <t>18330871796</t>
   </si>
   <si>
     <t>Desenvolvimento sistema Pré-lista EPI</t>
   </si>
   <si>
-    <t>35127</t>
+    <t>18379325252</t>
   </si>
   <si>
     <t>Altona || Estoque IMOB 39551 - Entradas + Consumo Diferente do Saldo</t>
   </si>
   <si>
-    <t>35276</t>
+    <t>18381357132</t>
   </si>
   <si>
     <t>Aplicação REtrabalho Inspeção - demora em carregar dados</t>
   </si>
   <si>
-    <t>35105</t>
+    <t>18379338408</t>
   </si>
   <si>
     <t>APONTAMENTO ELETRONICO MESA REDONDA UPR</t>
   </si>
   <si>
-    <t>35266</t>
+    <t>18379693409</t>
   </si>
   <si>
     <t>Remessa de Sucata para armazenagem no terreno Gaspar da Altona</t>
   </si>
   <si>
-    <t>35272</t>
+    <t>18379701434</t>
   </si>
   <si>
     <t>Contagem de Inventário</t>
   </si>
   <si>
-    <t>19909</t>
+    <t>18379246045</t>
   </si>
   <si>
     <t>Registro de pintura</t>
   </si>
   <si>
-    <t>34698</t>
+    <t>18379415159</t>
   </si>
   <si>
     <t>WMS</t>
   </si>
   <si>
-    <t>24746</t>
+    <t>18330872433</t>
   </si>
   <si>
     <t>Integração de faturamentos com eventos</t>
   </si>
   <si>
-    <t>34682</t>
+    <t>18330872485</t>
   </si>
   <si>
     <t>Registro campanha forno Arco - Reunião</t>
   </si>
   <si>
+    <t>18330872377</t>
+  </si>
+  <si>
     <t>Callback em aplicações WEB</t>
   </si>
   <si>
-    <t>35228</t>
+    <t>18379258168</t>
   </si>
   <si>
     <t>Melhoria no sistema de declaração de EPI</t>
   </si>
   <si>
-    <t>35224</t>
+    <t>18379264012</t>
   </si>
   <si>
     <t>PARADAS MANIPULADORES</t>
   </si>
   <si>
-    <t>34921</t>
+    <t>18379404194</t>
   </si>
   <si>
     <t>HORIMETRO MANIULADORES</t>
@@ -720,25 +756,25 @@
     <t>Sergio Schmidt</t>
   </si>
   <si>
-    <t>35023</t>
+    <t>18379366879</t>
   </si>
   <si>
     <t>SPS</t>
   </si>
   <si>
-    <t>35257</t>
+    <t>18379254622</t>
   </si>
   <si>
     <t>Integração do mapeamento digital com sistema do PCP</t>
   </si>
   <si>
-    <t>35046</t>
+    <t>18379363650</t>
   </si>
   <si>
     <t>Alteração sistema invoice: "Tipo de documento de declaração"</t>
   </si>
   <si>
-    <t>35018</t>
+    <t>18379369203</t>
   </si>
   <si>
     <t>MOVIMENTAÇÃO SETOR 501</t>
@@ -747,6 +783,9 @@
     <t>CRM - Atualizar IDERP nos registros já existentes</t>
   </si>
   <si>
+    <t>18236204145</t>
+  </si>
+  <si>
     <t>Criar documento na ordem de coleta (Puxar NF e invoice)</t>
   </si>
   <si>
@@ -756,66 +795,81 @@
     <t>CRM - Nova carga inicial de oportunidades</t>
   </si>
   <si>
+    <t>18236203841</t>
+  </si>
+  <si>
     <t>Desenvolver Aplicação Qlik Sense Dados Custeio - Chamado Principal</t>
   </si>
   <si>
     <t>CRM - Nova Carga de clientes</t>
   </si>
   <si>
-    <t>32353</t>
+    <t>18236204166</t>
   </si>
   <si>
     <t>Melhoria Sistema de Custeio - Usinagem Pintura - Revisão de Calculo</t>
   </si>
   <si>
-    <t xml:space="preserve">Alexandre, bom dia! Para Custeio Usinagem Pintura, ao invés de utilizar apontamentos de horas, valores do setor PINTURA (centro custo 8010) devem ser rateados somente para as sequências movimentadas no setor 3081. Critério de rateio deve ser proporcional de custo FTF dos setores 3081 + 3082 + 8010. </t>
-  </si>
-  <si>
-    <t>33191</t>
+    <t>18236204386</t>
   </si>
   <si>
     <t>Ticket - Programação</t>
   </si>
   <si>
+    <t>18236204182</t>
+  </si>
+  <si>
     <t>PDI - Inspeção - Cotas informadas.</t>
   </si>
   <si>
     <t>CRM - Testes unitários com usuário (oportunidade)</t>
   </si>
   <si>
+    <t>18236204425</t>
+  </si>
+  <si>
     <t>Criar restrição para edição do cadastro de pátio. Somente usuários do grupo "ADMYM " (copy)</t>
   </si>
   <si>
+    <t>18236204484</t>
+  </si>
+  <si>
     <t>Descrição da aplicação na barra de título e revisar descrições das telas</t>
   </si>
   <si>
-    <t>30903</t>
+    <t>18236204736</t>
   </si>
   <si>
     <t>Controle do status por declaração</t>
   </si>
   <si>
+    <t>18236204813</t>
+  </si>
+  <si>
     <t>Alterar ícones main menu</t>
   </si>
   <si>
+    <t>18382991092</t>
+  </si>
+  <si>
     <t>Ajuste calculo Metas Gerais Irog</t>
   </si>
   <si>
-    <t>18/11/2025</t>
-  </si>
-  <si>
-    <t>33588</t>
+    <t>10577840768</t>
   </si>
   <si>
     <t>Indicador Cobertura de Estoques</t>
   </si>
   <si>
-    <t>34171</t>
+    <t>10577990859</t>
   </si>
   <si>
     <t>Contagem Proformas</t>
   </si>
   <si>
+    <t>06/11/2025</t>
+  </si>
+  <si>
     <t>Impedimento</t>
   </si>
   <si>
@@ -828,88 +882,91 @@
     <t>Boa tarde Conforme conversamos, precisamos de um sistema dentro do WMS que faça a distribuição em tempo real do saldo do Estoque com a carteira. Conforme é realizado o faturamento, a carteira seja atualizada em tempo real, bem como a entrada e estorno do material. O sistema deve fornecer um relatóri</t>
   </si>
   <si>
-    <t>34693</t>
+    <t>10578066364</t>
   </si>
   <si>
     <t>Motivos de retrabalho da moldagem</t>
   </si>
   <si>
-    <t>34029</t>
+    <t>11/11/2025</t>
+  </si>
+  <si>
+    <t>18330872277</t>
   </si>
   <si>
     <t>Nota técnica 2025.002 - Alteração no XML da nota</t>
   </si>
   <si>
-    <t>33331</t>
+    <t>18236204753</t>
   </si>
   <si>
     <t>[APS] - Criação de campo no ERP CÓDIGO DISPOSITIVO</t>
   </si>
   <si>
-    <t>31270</t>
+    <t>02/11/2025</t>
+  </si>
+  <si>
+    <t>18236204884</t>
   </si>
   <si>
     <t>MELHORIAS FLUXO 109 REVISÕES</t>
   </si>
   <si>
-    <t>33841</t>
+    <t>18236205126</t>
   </si>
   <si>
     <t>MAPEAMENTO DIGITAL</t>
   </si>
   <si>
-    <t>33607</t>
+    <t>18236205600</t>
   </si>
   <si>
     <t>Gestão do fluxo por TPC - KOMATSU</t>
   </si>
   <si>
-    <t>33942</t>
+    <t>18236202691</t>
   </si>
   <si>
     <t>HISTÓRICO DE REVISÃO CHECKLIST DO AP119</t>
   </si>
   <si>
-    <t>34538</t>
+    <t>18236205706</t>
   </si>
   <si>
     <t>Planilhão Sense</t>
   </si>
   <si>
-    <t>33439</t>
+    <t>18236203258</t>
   </si>
   <si>
     <t>Processo ALTO IMPACTO</t>
   </si>
   <si>
-    <t>32536</t>
+    <t>18236203424</t>
   </si>
   <si>
     <t>DESENVOLVIMENTO DE CONTROLE DE DISPOSITIVOS DE USINAGEM</t>
   </si>
   <si>
-    <t>33651</t>
+    <t>18236203613</t>
   </si>
   <si>
     <t>Sequencia de Pre Produtivo</t>
   </si>
   <si>
-    <t>35327</t>
+    <t>18384346354</t>
   </si>
   <si>
     <t>MPO eletrônica UPR</t>
   </si>
   <si>
-    <t>19/11/2025</t>
-  </si>
-  <si>
     <t>Dashboard de Change Log - Governança de TI</t>
   </si>
   <si>
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2025-24</t>
+    <t>Out/2024</t>
   </si>
   <si>
     <t>Base</t>
@@ -1592,48 +1649,48 @@
         <v>36</v>
       </c>
       <c r="M4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N4" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="O4" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J5" s="2" t="s">
+      <c r="K5" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>44</v>
@@ -1653,51 +1710,51 @@
         <v>46</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>32</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>36</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
@@ -1709,10 +1766,10 @@
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>32</v>
@@ -1733,7 +1790,7 @@
         <v>36</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>27</v>
@@ -1744,7 +1801,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
@@ -1756,10 +1813,10 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>32</v>
@@ -1771,10 +1828,10 @@
         <v>22</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>25</v>
@@ -1791,7 +1848,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
@@ -1803,25 +1860,25 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K9" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>25</v>
@@ -1830,7 +1887,7 @@
         <v>26</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O9" s="2" t="s">
         <v>28</v>
@@ -1838,7 +1895,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -1850,10 +1907,10 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>32</v>
@@ -1874,18 +1931,18 @@
         <v>36</v>
       </c>
       <c r="M10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N10" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="N10" s="2" t="s">
+      <c r="O10" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1897,10 +1954,10 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>32</v>
@@ -1921,7 +1978,7 @@
         <v>36</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>27</v>
@@ -1932,7 +1989,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -1944,10 +2001,10 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>20</v>
@@ -1959,7 +2016,7 @@
         <v>22</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>24</v>
@@ -1971,7 +2028,7 @@
         <v>26</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O12" s="2" t="s">
         <v>28</v>
@@ -1979,7 +2036,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -1991,10 +2048,10 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>20</v>
@@ -2006,7 +2063,7 @@
         <v>22</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>24</v>
@@ -2018,7 +2075,7 @@
         <v>26</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O13" s="2" t="s">
         <v>28</v>
@@ -2026,34 +2083,34 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>24</v>
@@ -2062,10 +2119,10 @@
         <v>36</v>
       </c>
       <c r="M14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N14" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>28</v>
@@ -2073,22 +2130,22 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>32</v>
@@ -2103,24 +2160,24 @@
         <v>35</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="M15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N15" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="N15" s="2" t="s">
+      <c r="O15" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="O15" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>29</v>
+        <v>83</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -2132,10 +2189,10 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>32</v>
@@ -2167,43 +2224,43 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K17" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="L17" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="N17" s="2" t="s">
         <v>45</v>
@@ -2214,7 +2271,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
@@ -2226,10 +2283,10 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>32</v>
@@ -2250,18 +2307,18 @@
         <v>36</v>
       </c>
       <c r="M18" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N18" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="N18" s="2" t="s">
+      <c r="O18" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="O18" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
@@ -2273,10 +2330,10 @@
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>32</v>
@@ -2297,33 +2354,33 @@
         <v>36</v>
       </c>
       <c r="M19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N19" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="N19" s="2" t="s">
+      <c r="O19" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="O19" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>32</v>
@@ -2338,7 +2395,7 @@
         <v>35</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>25</v>
@@ -2347,15 +2404,15 @@
         <v>26</v>
       </c>
       <c r="N20" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O20" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="O20" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
@@ -2367,10 +2424,10 @@
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>32</v>
@@ -2382,10 +2439,10 @@
         <v>22</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>25</v>
@@ -2394,7 +2451,7 @@
         <v>26</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>28</v>
@@ -2402,7 +2459,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
@@ -2414,10 +2471,10 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>20</v>
@@ -2429,10 +2486,10 @@
         <v>22</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>25</v>
@@ -2444,42 +2501,42 @@
         <v>45</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>16</v>
+        <v>103</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>25</v>
@@ -2488,7 +2545,7 @@
         <v>26</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O23" s="2" t="s">
         <v>28</v>
@@ -2496,37 +2553,37 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>16</v>
+        <v>109</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>32</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>44</v>
@@ -2535,7 +2592,7 @@
         <v>26</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O24" s="2" t="s">
         <v>28</v>
@@ -2543,7 +2600,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -2555,10 +2612,10 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>32</v>
@@ -2579,18 +2636,18 @@
         <v>36</v>
       </c>
       <c r="M25" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N25" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="N25" s="2" t="s">
+      <c r="O25" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="O25" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
@@ -2602,10 +2659,10 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>20</v>
@@ -2617,27 +2674,27 @@
         <v>22</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>24</v>
+        <v>118</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
@@ -2649,10 +2706,10 @@
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>32</v>
@@ -2664,7 +2721,7 @@
         <v>22</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>24</v>
@@ -2676,7 +2733,7 @@
         <v>26</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O27" s="2" t="s">
         <v>28</v>
@@ -2684,7 +2741,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
@@ -2696,10 +2753,10 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>32</v>
@@ -2711,16 +2768,16 @@
         <v>22</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="N28" s="2" t="s">
         <v>45</v>
@@ -2731,7 +2788,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
@@ -2743,10 +2800,10 @@
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>32</v>
@@ -2758,7 +2815,7 @@
         <v>22</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>24</v>
@@ -2778,37 +2835,37 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>16</v>
+        <v>109</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>32</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>44</v>
@@ -2817,7 +2874,7 @@
         <v>26</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O30" s="2" t="s">
         <v>28</v>
@@ -2825,7 +2882,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
@@ -2837,10 +2894,10 @@
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>32</v>
@@ -2852,10 +2909,10 @@
         <v>22</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>44</v>
@@ -2864,7 +2921,7 @@
         <v>26</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O31" s="2" t="s">
         <v>28</v>
@@ -2872,7 +2929,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
@@ -2884,10 +2941,10 @@
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>20</v>
@@ -2899,19 +2956,19 @@
         <v>22</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>24</v>
+        <v>133</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="M32" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N32" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="N32" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="O32" s="2" t="s">
         <v>28</v>
@@ -2919,7 +2976,7 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>62</v>
+        <v>134</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
@@ -2931,10 +2988,10 @@
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>32</v>
@@ -2966,7 +3023,7 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
@@ -2978,10 +3035,10 @@
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>32</v>
@@ -2993,10 +3050,10 @@
         <v>22</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>25</v>
@@ -3005,7 +3062,7 @@
         <v>26</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O34" s="2" t="s">
         <v>28</v>
@@ -3013,7 +3070,7 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
@@ -3025,10 +3082,10 @@
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>32</v>
@@ -3040,7 +3097,7 @@
         <v>22</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>24</v>
@@ -3049,48 +3106,48 @@
         <v>36</v>
       </c>
       <c r="M35" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N35" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="N35" s="2" t="s">
+      <c r="O35" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="O35" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>16</v>
+        <v>109</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>32</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>44</v>
@@ -3099,7 +3156,7 @@
         <v>26</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O36" s="2" t="s">
         <v>28</v>
@@ -3107,7 +3164,7 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>16</v>
@@ -3119,10 +3176,10 @@
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>32</v>
@@ -3134,10 +3191,10 @@
         <v>22</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>24</v>
+        <v>147</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>25</v>
@@ -3154,43 +3211,43 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>36</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="N38" s="2" t="s">
         <v>27</v>
@@ -3201,7 +3258,7 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>16</v>
@@ -3213,10 +3270,10 @@
         <v>18</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>32</v>
@@ -3228,10 +3285,10 @@
         <v>22</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>24</v>
+        <v>157</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>25</v>
@@ -3240,15 +3297,15 @@
         <v>26</v>
       </c>
       <c r="N39" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O39" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="O39" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>66</v>
+        <v>158</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>16</v>
@@ -3260,10 +3317,10 @@
         <v>18</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>20</v>
@@ -3275,7 +3332,7 @@
         <v>22</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="K40" s="2" t="s">
         <v>24</v>
@@ -3287,7 +3344,7 @@
         <v>26</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O40" s="2" t="s">
         <v>28</v>
@@ -3295,7 +3352,7 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>16</v>
@@ -3307,10 +3364,10 @@
         <v>18</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>32</v>
@@ -3322,10 +3379,10 @@
         <v>22</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>24</v>
+        <v>147</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>44</v>
@@ -3334,7 +3391,7 @@
         <v>26</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O41" s="2" t="s">
         <v>28</v>
@@ -3342,7 +3399,7 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>16</v>
@@ -3354,10 +3411,10 @@
         <v>18</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>32</v>
@@ -3369,7 +3426,7 @@
         <v>22</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="K42" s="2" t="s">
         <v>24</v>
@@ -3378,45 +3435,45 @@
         <v>36</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>32</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="K43" s="2" t="s">
         <v>24</v>
@@ -3425,65 +3482,65 @@
         <v>36</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="M44" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N44" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="N44" s="2" t="s">
+      <c r="O44" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="O44" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>16</v>
@@ -3495,10 +3552,10 @@
         <v>18</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>32</v>
@@ -3513,13 +3570,13 @@
         <v>23</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>24</v>
+        <v>176</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>36</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="N45" s="2" t="s">
         <v>27</v>
@@ -3530,7 +3587,7 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>16</v>
@@ -3542,10 +3599,10 @@
         <v>18</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>20</v>
@@ -3557,10 +3614,10 @@
         <v>22</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>24</v>
+        <v>157</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>25</v>
@@ -3572,12 +3629,12 @@
         <v>27</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>164</v>
+        <v>180</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>16</v>
@@ -3589,10 +3646,10 @@
         <v>18</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>32</v>
@@ -3604,19 +3661,19 @@
         <v>22</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="K47" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="M47" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N47" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="N47" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="O47" s="2" t="s">
         <v>28</v>
@@ -3624,7 +3681,7 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>16</v>
@@ -3633,25 +3690,25 @@
         <v>30</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>32</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>170</v>
+        <v>21</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="K48" s="2" t="s">
         <v>24</v>
@@ -3663,15 +3720,15 @@
         <v>26</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>66</v>
+        <v>185</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>16</v>
@@ -3683,10 +3740,10 @@
         <v>18</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>20</v>
@@ -3698,7 +3755,7 @@
         <v>22</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="K49" s="2" t="s">
         <v>24</v>
@@ -3710,7 +3767,7 @@
         <v>26</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O49" s="2" t="s">
         <v>28</v>
@@ -3718,7 +3775,7 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>16</v>
@@ -3730,10 +3787,10 @@
         <v>18</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>32</v>
@@ -3745,19 +3802,19 @@
         <v>22</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>24</v>
+        <v>157</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="M50" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N50" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="N50" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="O50" s="2" t="s">
         <v>28</v>
@@ -3765,7 +3822,7 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>16</v>
@@ -3777,10 +3834,10 @@
         <v>18</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>32</v>
@@ -3792,10 +3849,10 @@
         <v>22</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>24</v>
+        <v>157</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>25</v>
@@ -3804,15 +3861,15 @@
         <v>26</v>
       </c>
       <c r="N51" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O51" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="O51" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>16</v>
@@ -3824,10 +3881,10 @@
         <v>18</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>32</v>
@@ -3839,7 +3896,7 @@
         <v>22</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K52" s="2" t="s">
         <v>24</v>
@@ -3859,7 +3916,7 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>16</v>
@@ -3868,28 +3925,28 @@
         <v>30</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>32</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>152</v>
+        <v>21</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>181</v>
+        <v>24</v>
       </c>
       <c r="L53" s="2" t="s">
         <v>25</v>
@@ -3906,7 +3963,7 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>16</v>
@@ -3915,34 +3972,34 @@
         <v>30</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>32</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>170</v>
+        <v>21</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>186</v>
+        <v>24</v>
       </c>
       <c r="L54" s="2" t="s">
         <v>36</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="N54" s="2" t="s">
         <v>45</v>
@@ -3953,7 +4010,7 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>16</v>
@@ -3965,10 +4022,10 @@
         <v>18</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>32</v>
@@ -3980,7 +4037,7 @@
         <v>22</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="K55" s="2" t="s">
         <v>24</v>
@@ -3989,7 +4046,7 @@
         <v>36</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="N55" s="2" t="s">
         <v>45</v>
@@ -4000,22 +4057,22 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>32</v>
@@ -4027,7 +4084,7 @@
         <v>22</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="K56" s="2" t="s">
         <v>24</v>
@@ -4039,7 +4096,7 @@
         <v>26</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O56" s="2" t="s">
         <v>28</v>
@@ -4047,7 +4104,7 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>16</v>
@@ -4059,10 +4116,10 @@
         <v>18</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>32</v>
@@ -4074,7 +4131,7 @@
         <v>22</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K57" s="2" t="s">
         <v>24</v>
@@ -4083,7 +4140,7 @@
         <v>36</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="N57" s="2" t="s">
         <v>45</v>
@@ -4094,46 +4151,46 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="M58" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N58" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="N58" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="O58" s="2" t="s">
         <v>28</v>
@@ -4141,22 +4198,22 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>20</v>
@@ -4168,10 +4225,10 @@
         <v>22</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L59" s="2" t="s">
         <v>25</v>
@@ -4180,7 +4237,7 @@
         <v>26</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O59" s="2" t="s">
         <v>28</v>
@@ -4188,7 +4245,7 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>16</v>
@@ -4200,10 +4257,10 @@
         <v>18</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>20</v>
@@ -4218,7 +4275,7 @@
         <v>23</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="L60" s="2" t="s">
         <v>25</v>
@@ -4235,22 +4292,22 @@
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>20</v>
@@ -4262,10 +4319,10 @@
         <v>22</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="L61" s="2" t="s">
         <v>25</v>
@@ -4282,7 +4339,7 @@
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>16</v>
@@ -4294,13 +4351,13 @@
         <v>18</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>21</v>
@@ -4329,7 +4386,7 @@
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>16</v>
@@ -4341,10 +4398,10 @@
         <v>18</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>32</v>
@@ -4356,7 +4413,7 @@
         <v>22</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K63" s="2" t="s">
         <v>24</v>
@@ -4365,7 +4422,7 @@
         <v>36</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="N63" s="2" t="s">
         <v>45</v>
@@ -4376,7 +4433,7 @@
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>16</v>
@@ -4388,10 +4445,10 @@
         <v>18</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>32</v>
@@ -4403,10 +4460,10 @@
         <v>22</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="L64" s="2" t="s">
         <v>25</v>
@@ -4415,7 +4472,7 @@
         <v>26</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O64" s="2" t="s">
         <v>28</v>
@@ -4423,7 +4480,7 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>16</v>
@@ -4435,10 +4492,10 @@
         <v>18</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>32</v>
@@ -4450,7 +4507,7 @@
         <v>22</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K65" s="2" t="s">
         <v>24</v>
@@ -4470,37 +4527,37 @@
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>32</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="L66" s="2" t="s">
         <v>25</v>
@@ -4517,7 +4574,7 @@
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>16</v>
@@ -4529,10 +4586,10 @@
         <v>18</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>20</v>
@@ -4544,10 +4601,10 @@
         <v>22</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="L67" s="2" t="s">
         <v>25</v>
@@ -4564,7 +4621,7 @@
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>16</v>
@@ -4576,10 +4633,10 @@
         <v>18</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>20</v>
@@ -4591,10 +4648,10 @@
         <v>22</v>
       </c>
       <c r="J68" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K68" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="K68" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="L68" s="2" t="s">
         <v>44</v>
@@ -4611,7 +4668,7 @@
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>16</v>
@@ -4623,10 +4680,10 @@
         <v>18</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>32</v>
@@ -4638,16 +4695,16 @@
         <v>22</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K69" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="N69" s="2" t="s">
         <v>45</v>
@@ -4658,7 +4715,7 @@
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>16</v>
@@ -4670,10 +4727,10 @@
         <v>18</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>32</v>
@@ -4685,10 +4742,10 @@
         <v>22</v>
       </c>
       <c r="J70" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K70" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="K70" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="L70" s="2" t="s">
         <v>25</v>
@@ -4705,22 +4762,22 @@
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>32</v>
@@ -4741,7 +4798,7 @@
         <v>36</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="N71" s="2" t="s">
         <v>27</v>
@@ -4752,7 +4809,7 @@
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>16</v>
@@ -4764,10 +4821,10 @@
         <v>18</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>32</v>
@@ -4799,7 +4856,7 @@
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>198</v>
+        <v>235</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>16</v>
@@ -4811,10 +4868,10 @@
         <v>18</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>32</v>
@@ -4835,7 +4892,7 @@
         <v>36</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="N73" s="2" t="s">
         <v>27</v>
@@ -4846,7 +4903,7 @@
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>16</v>
@@ -4858,10 +4915,10 @@
         <v>18</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>32</v>
@@ -4873,10 +4930,10 @@
         <v>22</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="L74" s="2" t="s">
         <v>25</v>
@@ -4893,7 +4950,7 @@
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>16</v>
@@ -4905,10 +4962,10 @@
         <v>18</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>32</v>
@@ -4920,7 +4977,7 @@
         <v>22</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K75" s="2" t="s">
         <v>24</v>
@@ -4940,7 +4997,7 @@
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>16</v>
@@ -4952,10 +5009,10 @@
         <v>18</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>32</v>
@@ -4967,10 +5024,10 @@
         <v>22</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>24</v>
+        <v>147</v>
       </c>
       <c r="L76" s="2" t="s">
         <v>44</v>
@@ -4987,43 +5044,43 @@
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>32</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="L77" s="2" t="s">
         <v>36</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="N77" s="2" t="s">
         <v>45</v>
@@ -5034,7 +5091,7 @@
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>16</v>
@@ -5046,10 +5103,10 @@
         <v>18</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>32</v>
@@ -5061,10 +5118,10 @@
         <v>22</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>24</v>
+        <v>118</v>
       </c>
       <c r="L78" s="2" t="s">
         <v>25</v>
@@ -5081,7 +5138,7 @@
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>16</v>
@@ -5093,10 +5150,10 @@
         <v>18</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>32</v>
@@ -5108,10 +5165,10 @@
         <v>22</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="L79" s="2" t="s">
         <v>25</v>
@@ -5128,7 +5185,7 @@
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>16</v>
@@ -5140,10 +5197,10 @@
         <v>18</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>32</v>
@@ -5155,10 +5212,10 @@
         <v>22</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>24</v>
+        <v>118</v>
       </c>
       <c r="L80" s="2" t="s">
         <v>44</v>
@@ -5175,7 +5232,7 @@
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>16</v>
@@ -5187,10 +5244,10 @@
         <v>18</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>32</v>
@@ -5202,10 +5259,10 @@
         <v>22</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>24</v>
+        <v>157</v>
       </c>
       <c r="L81" s="2" t="s">
         <v>25</v>
@@ -5222,46 +5279,46 @@
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="K82" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="M82" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N82" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="N82" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="O82" s="2" t="s">
         <v>28</v>
@@ -5269,22 +5326,22 @@
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>76</v>
+        <v>256</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>32</v>
@@ -5299,7 +5356,7 @@
         <v>35</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="L83" s="2" t="s">
         <v>25</v>
@@ -5308,54 +5365,54 @@
         <v>26</v>
       </c>
       <c r="N83" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O83" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="O83" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="K84" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="M84" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N84" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="N84" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="O84" s="2" t="s">
         <v>28</v>
@@ -5363,34 +5420,34 @@
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="K85" s="2" t="s">
         <v>24</v>
@@ -5399,10 +5456,10 @@
         <v>36</v>
       </c>
       <c r="M85" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N85" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="N85" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="O85" s="2" t="s">
         <v>28</v>
@@ -5410,7 +5467,7 @@
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>62</v>
+        <v>260</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>16</v>
@@ -5422,10 +5479,10 @@
         <v>18</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>20</v>
@@ -5446,45 +5503,45 @@
         <v>36</v>
       </c>
       <c r="M86" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N86" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="N86" s="2" t="s">
+      <c r="O86" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="O86" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="K87" s="2" t="s">
         <v>24</v>
@@ -5493,10 +5550,10 @@
         <v>36</v>
       </c>
       <c r="M87" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N87" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="N87" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="O87" s="2" t="s">
         <v>28</v>
@@ -5504,7 +5561,7 @@
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>16</v>
@@ -5513,22 +5570,22 @@
         <v>30</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>32</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>170</v>
+        <v>21</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="J88" s="2" t="s">
         <v>35</v>
@@ -5540,18 +5597,18 @@
         <v>36</v>
       </c>
       <c r="M88" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N88" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="N88" s="2" t="s">
+      <c r="O88" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="O88" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>16</v>
@@ -5563,10 +5620,10 @@
         <v>18</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>32</v>
@@ -5581,24 +5638,24 @@
         <v>35</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>24</v>
+        <v>118</v>
       </c>
       <c r="L89" s="2" t="s">
         <v>36</v>
       </c>
       <c r="M89" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N89" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="N89" s="2" t="s">
+      <c r="O89" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="O89" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>84</v>
+        <v>267</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>16</v>
@@ -5610,10 +5667,10 @@
         <v>18</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>32</v>
@@ -5634,45 +5691,45 @@
         <v>36</v>
       </c>
       <c r="M90" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N90" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="N90" s="2" t="s">
+      <c r="O90" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="O90" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="K91" s="2" t="s">
         <v>24</v>
@@ -5681,10 +5738,10 @@
         <v>36</v>
       </c>
       <c r="M91" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N91" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="N91" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="O91" s="2" t="s">
         <v>28</v>
@@ -5692,22 +5749,22 @@
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>76</v>
+        <v>270</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>256</v>
+        <v>271</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>256</v>
+        <v>271</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>32</v>
@@ -5731,30 +5788,30 @@
         <v>26</v>
       </c>
       <c r="N92" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O92" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="O92" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>76</v>
+        <v>272</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>257</v>
+        <v>273</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>257</v>
+        <v>273</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>32</v>
@@ -5778,30 +5835,30 @@
         <v>26</v>
       </c>
       <c r="N93" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O93" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="O93" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>259</v>
+        <v>275</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>259</v>
+        <v>275</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>32</v>
@@ -5822,33 +5879,33 @@
         <v>36</v>
       </c>
       <c r="M94" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N94" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="N94" s="2" t="s">
+      <c r="O94" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="O94" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>76</v>
+        <v>276</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>260</v>
+        <v>277</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>260</v>
+        <v>277</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>32</v>
@@ -5872,15 +5929,15 @@
         <v>26</v>
       </c>
       <c r="N95" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O95" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="O95" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>59</v>
+        <v>278</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>16</v>
@@ -5892,10 +5949,10 @@
         <v>18</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>32</v>
@@ -5907,7 +5964,7 @@
         <v>22</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>262</v>
+        <v>60</v>
       </c>
       <c r="K96" s="2" t="s">
         <v>24</v>
@@ -5919,7 +5976,7 @@
         <v>26</v>
       </c>
       <c r="N96" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O96" s="2" t="s">
         <v>28</v>
@@ -5927,7 +5984,7 @@
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>263</v>
+        <v>280</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>16</v>
@@ -5939,10 +5996,10 @@
         <v>18</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>264</v>
+        <v>281</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>264</v>
+        <v>281</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>20</v>
@@ -5954,19 +6011,19 @@
         <v>22</v>
       </c>
       <c r="J97" s="2" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="L97" s="2" t="s">
         <v>36</v>
       </c>
       <c r="M97" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N97" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="N97" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="O97" s="2" t="s">
         <v>28</v>
@@ -5974,7 +6031,7 @@
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>16</v>
@@ -5986,10 +6043,10 @@
         <v>18</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>266</v>
+        <v>283</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>266</v>
+        <v>283</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>32</v>
@@ -6001,19 +6058,19 @@
         <v>22</v>
       </c>
       <c r="J98" s="2" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>24</v>
+        <v>284</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>267</v>
+        <v>285</v>
       </c>
       <c r="M98" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N98" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="N98" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="O98" s="2" t="s">
         <v>28</v>
@@ -6021,46 +6078,46 @@
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>268</v>
+        <v>286</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>16</v>
+        <v>109</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>269</v>
+        <v>287</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>270</v>
+        <v>288</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="L99" s="2" t="s">
         <v>36</v>
       </c>
       <c r="M99" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N99" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="N99" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="O99" s="2" t="s">
         <v>28</v>
@@ -6068,7 +6125,7 @@
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>271</v>
+        <v>289</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>16</v>
@@ -6080,10 +6137,10 @@
         <v>18</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>272</v>
+        <v>290</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>272</v>
+        <v>290</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>32</v>
@@ -6095,10 +6152,10 @@
         <v>22</v>
       </c>
       <c r="J100" s="2" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>24</v>
+        <v>291</v>
       </c>
       <c r="L100" s="2" t="s">
         <v>25</v>
@@ -6107,7 +6164,7 @@
         <v>26</v>
       </c>
       <c r="N100" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O100" s="2" t="s">
         <v>28</v>
@@ -6115,43 +6172,43 @@
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>268</v>
+        <v>286</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>16</v>
+        <v>109</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>269</v>
+        <v>287</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>270</v>
+        <v>288</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J101" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K101" s="2" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="L101" s="2" t="s">
         <v>36</v>
       </c>
       <c r="M101" s="2" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="N101" s="2" t="s">
         <v>27</v>
@@ -6162,7 +6219,7 @@
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>273</v>
+        <v>292</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>16</v>
@@ -6174,10 +6231,10 @@
         <v>18</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>20</v>
@@ -6192,13 +6249,13 @@
         <v>23</v>
       </c>
       <c r="K102" s="2" t="s">
-        <v>24</v>
+        <v>118</v>
       </c>
       <c r="L102" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="M102" s="2" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="N102" s="2" t="s">
         <v>27</v>
@@ -6209,7 +6266,7 @@
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>275</v>
+        <v>294</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>16</v>
@@ -6221,10 +6278,10 @@
         <v>18</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>276</v>
+        <v>295</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>276</v>
+        <v>295</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>32</v>
@@ -6239,24 +6296,24 @@
         <v>35</v>
       </c>
       <c r="K103" s="2" t="s">
-        <v>24</v>
+        <v>296</v>
       </c>
       <c r="L103" s="2" t="s">
         <v>36</v>
       </c>
       <c r="M103" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N103" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="N103" s="2" t="s">
+      <c r="O103" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="O103" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>277</v>
+        <v>297</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>16</v>
@@ -6268,10 +6325,10 @@
         <v>18</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>278</v>
+        <v>298</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>278</v>
+        <v>298</v>
       </c>
       <c r="G104" s="2" t="s">
         <v>32</v>
@@ -6286,24 +6343,24 @@
         <v>35</v>
       </c>
       <c r="K104" s="2" t="s">
-        <v>24</v>
+        <v>296</v>
       </c>
       <c r="L104" s="2" t="s">
         <v>36</v>
       </c>
       <c r="M104" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N104" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="N104" s="2" t="s">
+      <c r="O104" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="O104" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>279</v>
+        <v>299</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>16</v>
@@ -6315,10 +6372,10 @@
         <v>18</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="G105" s="2" t="s">
         <v>32</v>
@@ -6333,7 +6390,7 @@
         <v>35</v>
       </c>
       <c r="K105" s="2" t="s">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="L105" s="2" t="s">
         <v>25</v>
@@ -6342,15 +6399,15 @@
         <v>26</v>
       </c>
       <c r="N105" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O105" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="O105" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>281</v>
+        <v>301</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>16</v>
@@ -6362,10 +6419,10 @@
         <v>18</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>282</v>
+        <v>302</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>282</v>
+        <v>302</v>
       </c>
       <c r="G106" s="2" t="s">
         <v>32</v>
@@ -6380,7 +6437,7 @@
         <v>35</v>
       </c>
       <c r="K106" s="2" t="s">
-        <v>24</v>
+        <v>118</v>
       </c>
       <c r="L106" s="2" t="s">
         <v>25</v>
@@ -6389,15 +6446,15 @@
         <v>26</v>
       </c>
       <c r="N106" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O106" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="O106" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>283</v>
+        <v>303</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>16</v>
@@ -6409,10 +6466,10 @@
         <v>18</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>284</v>
+        <v>304</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>284</v>
+        <v>304</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>32</v>
@@ -6427,7 +6484,7 @@
         <v>35</v>
       </c>
       <c r="K107" s="2" t="s">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="L107" s="2" t="s">
         <v>25</v>
@@ -6436,15 +6493,15 @@
         <v>26</v>
       </c>
       <c r="N107" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O107" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="O107" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="108" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>285</v>
+        <v>305</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>16</v>
@@ -6456,10 +6513,10 @@
         <v>18</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>286</v>
+        <v>306</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>286</v>
+        <v>306</v>
       </c>
       <c r="G108" s="2" t="s">
         <v>32</v>
@@ -6474,7 +6531,7 @@
         <v>35</v>
       </c>
       <c r="K108" s="2" t="s">
-        <v>24</v>
+        <v>118</v>
       </c>
       <c r="L108" s="2" t="s">
         <v>25</v>
@@ -6483,15 +6540,15 @@
         <v>26</v>
       </c>
       <c r="N108" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O108" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="O108" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="109" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>287</v>
+        <v>307</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>16</v>
@@ -6503,10 +6560,10 @@
         <v>18</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>288</v>
+        <v>308</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>288</v>
+        <v>308</v>
       </c>
       <c r="G109" s="2" t="s">
         <v>32</v>
@@ -6521,7 +6578,7 @@
         <v>35</v>
       </c>
       <c r="K109" s="2" t="s">
-        <v>24</v>
+        <v>157</v>
       </c>
       <c r="L109" s="2" t="s">
         <v>25</v>
@@ -6530,15 +6587,15 @@
         <v>26</v>
       </c>
       <c r="N109" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O109" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="O109" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="110" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>289</v>
+        <v>309</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>16</v>
@@ -6550,10 +6607,10 @@
         <v>18</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="G110" s="2" t="s">
         <v>32</v>
@@ -6568,24 +6625,24 @@
         <v>35</v>
       </c>
       <c r="K110" s="2" t="s">
-        <v>24</v>
+        <v>296</v>
       </c>
       <c r="L110" s="2" t="s">
         <v>36</v>
       </c>
       <c r="M110" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N110" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="N110" s="2" t="s">
+      <c r="O110" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="O110" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="111" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>16</v>
@@ -6597,10 +6654,10 @@
         <v>18</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>292</v>
+        <v>312</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>292</v>
+        <v>312</v>
       </c>
       <c r="G111" s="2" t="s">
         <v>32</v>
@@ -6615,24 +6672,24 @@
         <v>35</v>
       </c>
       <c r="K111" s="2" t="s">
-        <v>24</v>
+        <v>296</v>
       </c>
       <c r="L111" s="2" t="s">
         <v>36</v>
       </c>
       <c r="M111" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N111" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="N111" s="2" t="s">
+      <c r="O111" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="O111" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="112" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>293</v>
+        <v>313</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>16</v>
@@ -6644,10 +6701,10 @@
         <v>18</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>294</v>
+        <v>314</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>294</v>
+        <v>314</v>
       </c>
       <c r="G112" s="2" t="s">
         <v>32</v>
@@ -6659,10 +6716,10 @@
         <v>22</v>
       </c>
       <c r="J112" s="2" t="s">
-        <v>295</v>
+        <v>157</v>
       </c>
       <c r="K112" s="2" t="s">
-        <v>24</v>
+        <v>118</v>
       </c>
       <c r="L112" s="2" t="s">
         <v>25</v>
@@ -6671,7 +6728,7 @@
         <v>26</v>
       </c>
       <c r="N112" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O112" s="2" t="s">
         <v>28</v>
@@ -6690,23 +6747,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>297</v>
+        <v>316</v>
       </c>
       <c r="B2" t="s">
-        <v>298</v>
+        <v>317</v>
       </c>
       <c r="D2" t="s">
-        <v>299</v>
+        <v>318</v>
       </c>
       <c r="E2" t="s">
-        <v>300</v>
+        <v>319</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -6714,16 +6771,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>301</v>
+        <v>320</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>302</v>
+        <v>321</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>303</v>
+        <v>322</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>304</v>
+        <v>323</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -6734,15 +6791,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>151.75</v>
+        <v>23.48</v>
       </c>
       <c r="J5" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>305</v>
+        <v>324</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -6763,7 +6820,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>306</v>
+        <v>325</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -6794,12 +6851,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>307</v>
+        <v>326</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>301</v>
+        <v>320</v>
       </c>
       <c r="B2">
         <v>111</v>
@@ -6813,35 +6870,35 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>151.75</v>
+        <v>23.48</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>308</v>
+        <v>327</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>309</v>
+        <v>328</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>310</v>
+        <v>329</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>311</v>
+        <v>330</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>313</v>
+        <v>332</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -6849,7 +6906,7 @@
         <v>16</v>
       </c>
       <c r="B10">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="D10" t="s">
         <v>30</v>
@@ -6858,13 +6915,13 @@
         <v>93</v>
       </c>
       <c r="G10" t="s">
-        <v>314</v>
+        <v>333</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -6876,21 +6933,21 @@
         <v>52</v>
       </c>
       <c r="P10" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="Q10">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B11">
         <v>7</v>
       </c>
       <c r="D11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E11">
         <v>7</v>
@@ -6905,7 +6962,7 @@
         <v>26</v>
       </c>
       <c r="K11">
-        <v>61</v>
+        <v>111</v>
       </c>
       <c r="M11" t="s">
         <v>36</v>
@@ -6914,21 +6971,21 @@
         <v>36</v>
       </c>
       <c r="P11" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="Q11">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>136</v>
+        <v>109</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D12" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E12">
         <v>7</v>
@@ -6940,59 +6997,53 @@
         <v>80</v>
       </c>
       <c r="J12" t="s">
-        <v>316</v>
+        <v>335</v>
       </c>
       <c r="K12">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>267</v>
+        <v>285</v>
       </c>
       <c r="N12">
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="Q12">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>154</v>
+        <v>47</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="G13" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="H13">
         <v>2</v>
       </c>
       <c r="M13" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="N13">
         <v>8</v>
       </c>
-      <c r="P13" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q13">
-        <v>1</v>
-      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>194</v>
+        <v>103</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -7004,7 +7055,7 @@
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>317</v>
+        <v>336</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -7016,25 +7067,43 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="13:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>149</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
       <c r="M15" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="N15">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="13:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>169</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
       <c r="M16" t="s">
-        <v>318</v>
+        <v>337</v>
       </c>
       <c r="N16">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="13:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>205</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
       <c r="M17" t="s">
-        <v>319</v>
+        <v>338</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -7042,10 +7111,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -7053,7 +7122,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>321</v>
+        <v>340</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -7061,142 +7130,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>95</v>
+        <v>33</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>169</v>
+        <v>586</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>116</v>
+        <v>46</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="F22" s="2">
-        <v>169</v>
+        <v>586</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>117</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>129</v>
+        <v>56</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>109</v>
+        <v>586</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>130</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>178</v>
+        <v>63</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>100</v>
+        <v>586</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>179</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>586</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>19</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>29</v>
+        <v>71</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>586</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>31</v>
+        <v>74</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>586</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>586</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>586</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>586</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
